--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23700-2026 artfynd.xlsx
+++ b/artfynd/A 23700-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457055</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>136457052</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>136457051</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136457050</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136457053</v>
       </c>
       <c r="B6" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136457054</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136457069</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136457059</v>
       </c>
       <c r="B9" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>136457057</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>136457061</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
